--- a/research/traditional_assets/database/data/pakistan/pakistan_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_engineering_construction.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.42</v>
+        <v>-0.412</v>
       </c>
       <c r="G2">
-        <v>-1.810526315789474</v>
+        <v>-0.8321678321678322</v>
       </c>
       <c r="H2">
-        <v>-1.810526315789474</v>
+        <v>-0.8321678321678322</v>
       </c>
       <c r="I2">
-        <v>-1.878947368421052</v>
+        <v>-0.9160839160839161</v>
       </c>
       <c r="J2">
-        <v>-1.878947368421052</v>
+        <v>-0.9160839160839161</v>
       </c>
       <c r="K2">
-        <v>-0.067</v>
+        <v>-0.104</v>
       </c>
       <c r="L2">
-        <v>-0.3526315789473685</v>
+        <v>-0.7272727272727273</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.004848484848484848</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-0.01413502109704641</v>
+        <v>-0.0224622030237581</v>
       </c>
       <c r="X2">
-        <v>0.1099430593572797</v>
+        <v>0.1975769526180427</v>
       </c>
       <c r="Y2">
-        <v>-0.1240780804543261</v>
+        <v>-0.2200391556418008</v>
       </c>
       <c r="Z2">
-        <v>0.04012671594508976</v>
+        <v>0.02980408503543143</v>
       </c>
       <c r="AA2">
-        <v>-0.07539598732840548</v>
+        <v>-0.02730304293455607</v>
       </c>
       <c r="AB2">
-        <v>0.105047275492435</v>
+        <v>0.1818417336300107</v>
       </c>
       <c r="AC2">
-        <v>-0.1804432628208405</v>
+        <v>-0.2091447765645668</v>
       </c>
       <c r="AD2">
-        <v>0.176</v>
+        <v>0.138</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.176</v>
+        <v>0.138</v>
       </c>
       <c r="AG2">
-        <v>0.168</v>
+        <v>0.138</v>
       </c>
       <c r="AH2">
-        <v>0.0963855421686747</v>
+        <v>0.1684981684981685</v>
       </c>
       <c r="AI2">
-        <v>0.03662089055347482</v>
+        <v>0.03900508762012437</v>
       </c>
       <c r="AJ2">
-        <v>0.0924092409240924</v>
+        <v>0.1684981684981685</v>
       </c>
       <c r="AK2">
-        <v>0.0350145894122551</v>
+        <v>0.03900508762012437</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0.5176470588235293</v>
+        <v>-1.169491525423729</v>
       </c>
       <c r="AP2">
-        <v>-0.4941176470588234</v>
+        <v>-1.169491525423729</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.42</v>
+        <v>-0.412</v>
       </c>
       <c r="G3">
-        <v>-1.810526315789474</v>
+        <v>-0.8321678321678322</v>
       </c>
       <c r="H3">
-        <v>-1.810526315789474</v>
+        <v>-0.8321678321678322</v>
       </c>
       <c r="I3">
-        <v>-1.878947368421052</v>
+        <v>-0.9160839160839161</v>
       </c>
       <c r="J3">
-        <v>-1.878947368421052</v>
+        <v>-0.9160839160839161</v>
       </c>
       <c r="K3">
-        <v>-0.067</v>
+        <v>-0.104</v>
       </c>
       <c r="L3">
-        <v>-0.3526315789473685</v>
+        <v>-0.7272727272727273</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.004848484848484848</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.01413502109704641</v>
+        <v>-0.0224622030237581</v>
       </c>
       <c r="X3">
-        <v>0.1099430593572797</v>
+        <v>0.1975769526180427</v>
       </c>
       <c r="Y3">
-        <v>-0.1240780804543261</v>
+        <v>-0.2200391556418008</v>
       </c>
       <c r="Z3">
-        <v>0.04012671594508976</v>
+        <v>0.02980408503543143</v>
       </c>
       <c r="AA3">
-        <v>-0.07539598732840548</v>
+        <v>-0.02730304293455607</v>
       </c>
       <c r="AB3">
-        <v>0.105047275492435</v>
+        <v>0.1818417336300107</v>
       </c>
       <c r="AC3">
-        <v>-0.1804432628208405</v>
+        <v>-0.2091447765645668</v>
       </c>
       <c r="AD3">
-        <v>0.176</v>
+        <v>0.138</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.176</v>
+        <v>0.138</v>
       </c>
       <c r="AG3">
-        <v>0.168</v>
+        <v>0.138</v>
       </c>
       <c r="AH3">
-        <v>0.0963855421686747</v>
+        <v>0.1684981684981685</v>
       </c>
       <c r="AI3">
-        <v>0.03662089055347482</v>
+        <v>0.03900508762012437</v>
       </c>
       <c r="AJ3">
-        <v>0.0924092409240924</v>
+        <v>0.1684981684981685</v>
       </c>
       <c r="AK3">
-        <v>0.0350145894122551</v>
+        <v>0.03900508762012437</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0.5176470588235293</v>
+        <v>-1.169491525423729</v>
       </c>
       <c r="AP3">
-        <v>-0.4941176470588234</v>
+        <v>-1.169491525423729</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_engineering_construction.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.412</v>
+        <v>-0.229</v>
+      </c>
+      <c r="E2">
+        <v>-0.168</v>
       </c>
       <c r="G2">
-        <v>-0.8321678321678322</v>
+        <v>0.0581529989964748</v>
       </c>
       <c r="H2">
-        <v>-0.8321678321678322</v>
+        <v>0.0581529989964748</v>
       </c>
       <c r="I2">
-        <v>-0.9160839160839161</v>
+        <v>0.006664436610657952</v>
       </c>
       <c r="J2">
-        <v>-0.9160839160839161</v>
+        <v>0.004998327457993465</v>
       </c>
       <c r="K2">
-        <v>-0.104</v>
+        <v>-0.249</v>
       </c>
       <c r="L2">
-        <v>-0.7272727272727273</v>
+        <v>-0.006407122455806294</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +633,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>-0.0224622030237581</v>
+        <v>0.02790613718411553</v>
       </c>
       <c r="X2">
-        <v>0.1975769526180427</v>
-      </c>
-      <c r="Y2">
-        <v>-0.2200391556418008</v>
+        <v>0.194843925894133</v>
       </c>
       <c r="Z2">
-        <v>0.02980408503543143</v>
-      </c>
-      <c r="AA2">
-        <v>-0.02730304293455607</v>
+        <v>10.87076923076923</v>
       </c>
       <c r="AB2">
-        <v>0.1818417336300107</v>
-      </c>
-      <c r="AC2">
-        <v>-0.2091447765645668</v>
+        <v>0.1900764701748747</v>
       </c>
       <c r="AD2">
-        <v>0.138</v>
+        <v>1.324</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.138</v>
+        <v>1.324</v>
       </c>
       <c r="AG2">
-        <v>0.138</v>
+        <v>0.551</v>
       </c>
       <c r="AH2">
-        <v>0.1684981684981685</v>
+        <v>0.04561742006615215</v>
       </c>
       <c r="AI2">
-        <v>0.03900508762012437</v>
+        <v>0.06097448650640139</v>
       </c>
       <c r="AJ2">
-        <v>0.1684981684981685</v>
+        <v>0.01950373438108386</v>
       </c>
       <c r="AK2">
-        <v>0.03900508762012437</v>
+        <v>0.02631201948331026</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.778</v>
       </c>
       <c r="AN2">
-        <v>-1.169491525423729</v>
+        <v>1.11541701769166</v>
       </c>
       <c r="AP2">
-        <v>-1.169491525423729</v>
+        <v>0.4641954507160911</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.3329048843187661</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +695,231 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Hinopak Motors Limited (KASE:HINO)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Engineering/Construction</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.151</v>
+      </c>
+      <c r="G3">
+        <v>0.05736434108527132</v>
+      </c>
+      <c r="H3">
+        <v>0.05736434108527132</v>
+      </c>
+      <c r="I3">
+        <v>0.005503875968992248</v>
+      </c>
+      <c r="J3">
+        <v>0.002751937984496124</v>
+      </c>
+      <c r="K3">
+        <v>-0.316</v>
+      </c>
+      <c r="L3">
+        <v>-0.008165374677002584</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.766</v>
+      </c>
+      <c r="V3">
+        <v>0.02901515151515152</v>
+      </c>
+      <c r="X3">
+        <v>0.1930524920263746</v>
+      </c>
+      <c r="AB3">
+        <v>0.1895373915374875</v>
+      </c>
+      <c r="AD3">
+        <v>1.22</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.22</v>
+      </c>
+      <c r="AG3">
+        <v>0.454</v>
+      </c>
+      <c r="AH3">
+        <v>0.0441708906589428</v>
+      </c>
+      <c r="AI3">
+        <v>0.06482465462274176</v>
+      </c>
+      <c r="AJ3">
+        <v>0.01690623370819989</v>
+      </c>
+      <c r="AK3">
+        <v>0.02514678187659244</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-0.778</v>
+      </c>
+      <c r="AN3">
+        <v>1.079646017699115</v>
+      </c>
+      <c r="AP3">
+        <v>0.4017699115044248</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.2737789203084833</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Gammon Pakistan Limited (KASE:GAMON)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Engineering/Construction</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.412</v>
-      </c>
-      <c r="G3">
-        <v>-0.8321678321678322</v>
-      </c>
-      <c r="H3">
-        <v>-0.8321678321678322</v>
-      </c>
-      <c r="I3">
-        <v>-0.9160839160839161</v>
-      </c>
-      <c r="J3">
-        <v>-0.9160839160839161</v>
-      </c>
-      <c r="K3">
-        <v>-0.104</v>
-      </c>
-      <c r="L3">
-        <v>-0.7272727272727273</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>-0.0224622030237581</v>
-      </c>
-      <c r="X3">
-        <v>0.1975769526180427</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2200391556418008</v>
-      </c>
-      <c r="Z3">
-        <v>0.02980408503543143</v>
-      </c>
-      <c r="AA3">
-        <v>-0.02730304293455607</v>
-      </c>
-      <c r="AB3">
-        <v>0.1818417336300107</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2091447765645668</v>
-      </c>
-      <c r="AD3">
-        <v>0.138</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.138</v>
-      </c>
-      <c r="AG3">
-        <v>0.138</v>
-      </c>
-      <c r="AH3">
-        <v>0.1684981684981685</v>
-      </c>
-      <c r="AI3">
-        <v>0.03900508762012437</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1684981684981685</v>
-      </c>
-      <c r="AK3">
-        <v>0.03900508762012437</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>-1.169491525423729</v>
-      </c>
-      <c r="AP3">
-        <v>-1.169491525423729</v>
+      <c r="D4">
+        <v>-0.307</v>
+      </c>
+      <c r="E4">
+        <v>-0.168</v>
+      </c>
+      <c r="G4">
+        <v>0.245398773006135</v>
+      </c>
+      <c r="H4">
+        <v>0.245398773006135</v>
+      </c>
+      <c r="I4">
+        <v>0.2822085889570552</v>
+      </c>
+      <c r="J4">
+        <v>0.2822085889570552</v>
+      </c>
+      <c r="K4">
+        <v>0.067</v>
+      </c>
+      <c r="L4">
+        <v>0.4110429447852761</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.007</v>
+      </c>
+      <c r="V4">
+        <v>0.005384615384615384</v>
+      </c>
+      <c r="W4">
+        <v>0.01942028985507246</v>
+      </c>
+      <c r="X4">
+        <v>0.1966353597618913</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1772150699068188</v>
+      </c>
+      <c r="Z4">
+        <v>0.04559440559440559</v>
+      </c>
+      <c r="AA4">
+        <v>0.01286713286713287</v>
+      </c>
+      <c r="AB4">
+        <v>0.190615548812262</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1777484159451291</v>
+      </c>
+      <c r="AD4">
+        <v>0.104</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.104</v>
+      </c>
+      <c r="AG4">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AI4">
+        <v>0.0359364201796821</v>
+      </c>
+      <c r="AJ4">
+        <v>0.06943450250536864</v>
+      </c>
+      <c r="AK4">
+        <v>0.03359889158295808</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>1.824561403508772</v>
+      </c>
+      <c r="AP4">
+        <v>1.701754385964912</v>
       </c>
     </row>
   </sheetData>
